--- a/artfynd/A 53216-2025 artfynd.xlsx
+++ b/artfynd/A 53216-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111974997</v>
+        <v>111975000</v>
       </c>
       <c r="B2" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329193</v>
+        <v>329039</v>
       </c>
       <c r="R2" t="n">
-        <v>6596064</v>
+        <v>6596278</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111963063</v>
+        <v>111975002</v>
       </c>
       <c r="B3" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,38 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Berget (Berget), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329059</v>
+        <v>329079</v>
       </c>
       <c r="R3" t="n">
-        <v>6596048</v>
+        <v>6596073</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,19 +840,9 @@
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111963093</v>
+        <v>111963063</v>
       </c>
       <c r="B4" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -927,14 +901,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Berget (Berget), Vrm</t>
+          <t>Berget, Berget, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329072</v>
+        <v>329059</v>
       </c>
       <c r="R4" t="n">
-        <v>6596021</v>
+        <v>6596048</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,7 +940,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -976,7 +950,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,53 +977,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111975002</v>
+        <v>111963093</v>
       </c>
       <c r="B5" t="n">
-        <v>90814</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Berget (Berget), Vrm</t>
+          <t>Berget, Berget, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329079</v>
+        <v>329072</v>
       </c>
       <c r="R5" t="n">
-        <v>6596072</v>
+        <v>6596021</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,9 +1046,19 @@
           <t>2023-09-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,15 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111963153</v>
+        <v>111963142</v>
       </c>
       <c r="B6" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,18 +1113,27 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Berget (Berget), Vrm</t>
+          <t>Åsen, Åsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>329148</v>
+        <v>329149</v>
       </c>
       <c r="R6" t="n">
-        <v>6596034</v>
+        <v>6596028</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1181,7 +1165,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1175,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,15 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111974999</v>
+        <v>111963147</v>
       </c>
       <c r="B7" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,20 +1230,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Berget (Berget), Vrm</t>
+          <t>Berget, Berget, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>329176</v>
+        <v>329147</v>
       </c>
       <c r="R7" t="n">
-        <v>6596063</v>
+        <v>6596033</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,9 +1284,19 @@
           <t>2023-09-08</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,53 +1323,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111975000</v>
+        <v>111963153</v>
       </c>
       <c r="B8" t="n">
-        <v>90816</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Berget (Berget), Vrm</t>
+          <t>Berget, Berget, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>329039</v>
+        <v>329148</v>
       </c>
       <c r="R8" t="n">
-        <v>6596278</v>
+        <v>6596035</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,9 +1392,19 @@
           <t>2023-09-08</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111963147</v>
+        <v>111974997</v>
       </c>
       <c r="B9" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,34 +1459,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Berget (Berget), Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>329147</v>
+        <v>329192</v>
       </c>
       <c r="R9" t="n">
-        <v>6596032</v>
+        <v>6596064</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,19 +1499,9 @@
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,15 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111963142</v>
+        <v>111974999</v>
       </c>
       <c r="B10" t="n">
-        <v>96735</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,30 +1556,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åsen (Åsen), Vrm</t>
+          <t>Berget (Berget), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>329149</v>
+        <v>329177</v>
       </c>
       <c r="R10" t="n">
-        <v>6596028</v>
+        <v>6596062</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,19 +1596,9 @@
           <t>2023-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,6 +1622,131 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113457686</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Berget, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>329147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6596032</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Holmedal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>S-Årj-0359</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Även RT90: 6600421 - 1283500 resp. 6600422 - 1283516, noggrannhet 15 m, utan antal angivet.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
